--- a/stick-world/config/excel/运输数据.xlsx
+++ b/stick-world/config/excel/运输数据.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="运输载体" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="道路" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="载具列表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -436,98 +437,108 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name_zh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>speed</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>capacity</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>cost_per_km</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>carrier_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>stamina_modifier</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>capacity_per_unit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>requires_road</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>terrain_penalty</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>unlock_tech</t>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>唯一ID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>速度</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>运量</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>单位成本</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>载体类型</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>耐力节省倍率(越高越省力)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>单位运量(每运输者)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>需要道路</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>地形惩罚</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>解锁科技</t>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>car_human</t>
+          <t>car_none</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>人力搬运</t>
+          <t>徒手搬运</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -537,12 +548,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>纯靠火柴人耐力，巨人运量极大</t>
         </is>
       </c>
     </row>
@@ -559,12 +575,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>beast</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -574,12 +590,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>山地减速</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>驼兽自身耐力+载重，需驯服</t>
         </is>
       </c>
     </row>
@@ -596,12 +617,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>wagon</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -611,123 +632,185 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tech_wheel</t>
+          <t>高地/山地不可用</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>驮兽+车=节省耐力，需道路；可载人，支持两班倒轮流驾驶</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>car_river</t>
+          <t>car_sled</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>河船</t>
+          <t>雪橇</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>sled</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>water_only</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tech_sailing</t>
+          <t>仅雪地可用</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>雪地火柴人耐力加成地区专用；可载人，支持两班倒轮流驾驶</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>car_ship</t>
+          <t>car_boat</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>海船</t>
+          <t>小船</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ocean_only</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tech_seafaring</t>
+          <t>仅水域</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>沿河流/海岸移动，节省大量耐力；可载人，支持两班倒轮流驾驶</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>car_magic</t>
+          <t>car_ship</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>魔法传送阵</t>
+          <t>海船</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>ship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tech_teleport</t>
+          <t>仅海域</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>远洋运输，需港口；可载人，支持两班倒轮流驾驶</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>car_giant</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>奴役巨人</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>山地无惩罚</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>铁链+军事人员押送，巨人耐力极大</t>
         </is>
       </c>
     </row>
@@ -742,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -756,98 +839,78 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name_zh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>speed_bonus</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>build_cost_stone</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>build_cost_wood</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>build_time</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>maintenance</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>unlock_tech</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>stamina_bonus</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>build_material</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>build_workload</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>唯一ID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>速度加成</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>石料消耗</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>木材消耗</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>建造时间</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>维护成本</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>解锁科技</t>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>耐力节省加成(叠加载体)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>建造材料</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>建造工程量</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>road_dirt</t>
+          <t>road_trail</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>土路</t>
+          <t>小径</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -857,39 +920,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>无(自然形成)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>重复走出来的路，无建造成本</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>road_stone</t>
+          <t>road_dirt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>石板路</t>
+          <t>土路</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -899,7 +952,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>木材,石料</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -909,29 +962,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>tech_stone_road</t>
+          <t>需要施工队平整路面</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>road_highway</t>
+          <t>road_stone</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>帝国大道</t>
+          <t>石板路</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -941,7 +984,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>石料</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -951,59 +994,557 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>tech_imperial_road</t>
+          <t>耐久好，雨雪不影响通行</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>canal</t>
+          <t>road_bridge</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>运河</t>
+          <t>桥梁</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.0x</t>
+          <t>3.0x(跨河)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>木材,石料</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>跨越河流，关键基建</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>port</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>启用海船运输</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>木材,石料</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>沿海节点，解锁海船</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name_zh</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>carrier_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>can_carry_people</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>passenger_capacity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cargo_capacity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>build_material</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>build_workload</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>唯一ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>所用运输方式</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>可载人</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>载人数量</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>载货量</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>攻击力(战斗载具)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>建造材料</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>建造工程量</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>veh_handcart</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>手推车</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>wagon</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>木材</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>单人推行，纯货运</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>veh_wagon</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>货运马车</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>wagon</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>木材,金属</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>可载人载货，支持两班倒轮流驾驶</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>veh_sled</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>雪橇</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sled</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>木材</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>雪地专用，可载人，支持两班倒</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>veh_transport_boat</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>运输船</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>木材</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>沿河运输，可载人，支持两班倒</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>veh_cargo_ship</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>货船</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ship</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>木材,金属</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>远洋运输，可载人，支持两班倒</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>veh_catapult</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>投石车</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>wagon</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>木材,金属</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>tech_canal</t>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>攻城武器，攻击力 30，需拖拽移动。攻击模式硬编码</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>veh_siege_tower</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>攻城塔</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>wagon</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>木材,金属</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>搭载士兵越过城墙，需拖拽移动</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>veh_ram</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>冲车</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>wagon</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>木材,金属</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>攻城武器，攻击力 50(对城门加成)，攻击模式硬编码</t>
         </is>
       </c>
     </row>

--- a/stick-world/config/excel/运输数据.xlsx
+++ b/stick-world/config/excel/运输数据.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="运输载体" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="道路" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="载具列表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="carriers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="roads" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="vehicles" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -439,294 +439,195 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name_zh</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>carrier_type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>stamina_modifier</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>capacity_per_unit</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>requires_road</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>terrain_penalty</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>notes</t>
+          <t>#output_dir: logistics</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>唯一ID</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>name_zh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>载体类型</t>
+          <t>speed</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>耐力节省倍率(越高越省力)</t>
+          <t>capacity</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>单位运量(每运输者)</t>
+          <t>cost_per_km</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>需要道路</t>
+          <t>terrain_penalty</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>地形惩罚</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>unlock_tech</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>car_none</t>
+          <t>唯一ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>徒手搬运</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>speed</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>capacity</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>cost_per_km</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>地形惩罚</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>纯靠火柴人耐力，巨人运量极大</t>
+          <t>unlock_tech</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>car_beast</t>
+          <t>car_human</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>驮兽</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>beast</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>人力搬运</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>山地减速</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>驼兽自身耐力+载重，需驯服</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>car_wagon</t>
+          <t>car_beast</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>马车</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>wagon</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>驮兽</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>高地/山地不可用</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>驮兽+车=节省耐力，需道路；可载人，支持两班倒轮流驾驶</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>car_sled</t>
+          <t>car_wagon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>雪橇</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>sled</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>马车</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仅雪地可用</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>雪地火柴人耐力加成地区专用；可载人，支持两班倒轮流驾驶</t>
+          <t>tech_wheel</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>car_boat</t>
+          <t>car_river</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小船</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>boat</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+          <t>河船</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>80</v>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>water_only</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅水域</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>沿河流/海岸移动，节省大量耐力；可载人，支持两班倒轮流驾驶</t>
+          <t>tech_sailing</t>
         </is>
       </c>
     </row>
@@ -741,76 +642,49 @@
           <t>海船</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ship</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" t="n">
+        <v>20</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>ocean_only</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅海域</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>远洋运输，需港口；可载人，支持两班倒轮流驾驶</t>
+          <t>tech_seafaring</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>car_giant</t>
+          <t>car_magic</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>奴役巨人</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>giant</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
+          <t>魔法传送阵</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>山地无惩罚</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>铁链+军事人员押送，巨人耐力极大</t>
+          <t>tech_teleport</t>
         </is>
       </c>
     </row>
@@ -825,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -841,96 +715,91 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name_zh</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>stamina_bonus</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>build_material</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>build_workload</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>notes</t>
+          <t>#output_dir: logistics</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>唯一ID</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>name_zh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>耐力节省加成(叠加载体)</t>
+          <t>speed_bonus</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>建造材料</t>
+          <t>build_cost_stone</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>建造工程量</t>
+          <t>build_cost_wood</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>build_time</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>unlock_tech</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>road_trail</t>
+          <t>唯一ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>小径</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.2x</t>
+          <t>speed_bonus</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>无(自然形成)</t>
+          <t>build_cost_stone</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>build_cost_wood</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>重复走出来的路，无建造成本</t>
+          <t>build_time</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>unlock_tech</t>
         </is>
       </c>
     </row>
@@ -947,23 +816,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.5x</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>木材,石料</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>需要施工队平整路面</t>
-        </is>
+          <t>1.2x</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -979,86 +845,92 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.0x</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>石料</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>耐久好，雨雪不影响通行</t>
+          <t>1.5x</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>tech_stone_road</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>road_bridge</t>
+          <t>road_highway</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>桥梁</t>
+          <t>帝国大道</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.0x(跨河)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>木材,石料</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>跨越河流，关键基建</t>
+          <t>2.0x</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>tech_imperial_road</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>port</t>
+          <t>canal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>运河</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>启用海船运输</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>木材,石料</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>沿海节点，解锁海船</t>
+          <t>3.0x</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>tech_canal</t>
         </is>
       </c>
     </row>
@@ -1073,168 +945,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name_zh</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>carrier_type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>can_carry_people</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>passenger_capacity</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>cargo_capacity</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>build_material</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>build_workload</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>notes</t>
+          <t>#output_dir: logistics</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>唯一ID</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>name_zh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>所用运输方式</t>
+          <t>carrier_type</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>可载人</t>
+          <t>can_carry_people</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>载人数量</t>
+          <t>passenger_capacity</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>载货量</t>
+          <t>cargo_capacity</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>攻击力(战斗载具)</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>建造材料</t>
+          <t>build_material</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>建造工程量</t>
+          <t>build_workload</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>notes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>veh_handcart</t>
+          <t>唯一ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>手推车</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wagon</t>
+          <t>所用运输方式</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
+          <t>可载人</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>载人数量</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>载货量</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>攻击力(战斗载具)</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>木材</t>
+          <t>建造材料</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>建造工程量</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>单人推行，纯货运</t>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>veh_wagon</t>
+          <t>veh_handcart</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>货运马车</t>
+          <t>手推车</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1244,48 +1077,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>木材,金属</t>
+          <t>木材</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>可载人载货，支持两班倒轮流驾驶</t>
+          <t>单人推行，纯货运</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>veh_sled</t>
+          <t>veh_wagon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>雪橇</t>
+          <t>货运马车</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sled</t>
+          <t>wagon</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1297,41 +1130,41 @@
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>木材</t>
+          <t>木材,金属</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>雪地专用，可载人，支持两班倒</t>
+          <t>可载人载货，支持两班倒轮流驾驶</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>veh_transport_boat</t>
+          <t>veh_sled</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>运输船</t>
+          <t>雪橇</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sled</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1340,10 +1173,10 @@
         </is>
       </c>
       <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
         <v>4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1355,29 +1188,29 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>沿河运输，可载人，支持两班倒</t>
+          <t>雪地专用，可载人，支持两班倒</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>veh_cargo_ship</t>
+          <t>veh_transport_boat</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>货船</t>
+          <t>运输船</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ship</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1386,60 +1219,60 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>木材,金属</t>
+          <t>木材</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>远洋运输，可载人，支持两班倒</t>
+          <t>沿河运输，可载人，支持两班倒</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>veh_catapult</t>
+          <t>veh_cargo_ship</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>投石车</t>
+          <t>货船</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>wagon</t>
+          <t>ship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>30</v>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>木材,金属</t>
@@ -1447,24 +1280,24 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>攻城武器，攻击力 30，需拖拽移动。攻击模式硬编码</t>
+          <t>远洋运输，可载人，支持两班倒</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>veh_siege_tower</t>
+          <t>veh_catapult</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>攻城塔</t>
+          <t>投石车</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1474,17 +1307,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1493,24 +1326,24 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>搭载士兵越过城墙，需拖拽移动</t>
+          <t>攻城武器，攻击力 30，需拖拽移动。攻击模式硬编码</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>veh_ram</t>
+          <t>veh_siege_tower</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>冲车</t>
+          <t>攻城塔</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1520,29 +1353,75 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>木材,金属</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>搭载士兵越过城墙，需拖拽移动</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>veh_ram</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>冲车</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>wagon</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>50</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>木材,金属</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>攻城武器，攻击力 50(对城门加成)，攻击模式硬编码</t>
         </is>
